--- a/output/tables/universal_sm_hybrid/hybrid_headline.xlsx
+++ b/output/tables/universal_sm_hybrid/hybrid_headline.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">scenario</t>
   </si>
@@ -50,13 +50,10 @@
     <t xml:space="preserve">headline_universal_account_uniform</t>
   </si>
   <si>
-    <t xml:space="preserve">sens_no_auto_5_7pct</t>
+    <t xml:space="preserve">sens_auto_enroll_80pct</t>
   </si>
   <si>
     <t xml:space="preserve">sensitivity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sens_auto_enroll_80pct</t>
   </si>
   <si>
     <t xml:space="preserve">sens_full_participation_100pct</t>
@@ -422,13 +419,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>46.06</v>
+        <v>46.07</v>
       </c>
       <c r="D2" t="n">
         <v>27.54</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5979</v>
+        <v>0.5978</v>
       </c>
       <c r="F2" t="n">
         <v>543</v>
@@ -503,19 +500,19 @@
         <v>46.07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.63</v>
+        <v>36.85</v>
       </c>
       <c r="E5" t="n">
-        <v>0.057</v>
+        <v>0.8</v>
       </c>
       <c r="F5" t="n">
         <v>541</v>
       </c>
       <c r="G5" t="n">
-        <v>1421</v>
+        <v>19938</v>
       </c>
       <c r="H5" t="n">
-        <v>1.42</v>
+        <v>19.94</v>
       </c>
     </row>
     <row r="6">
@@ -529,44 +526,18 @@
         <v>46.07</v>
       </c>
       <c r="D6" t="n">
-        <v>36.85</v>
+        <v>46.07</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>541</v>
       </c>
       <c r="G6" t="n">
-        <v>19938</v>
+        <v>24923</v>
       </c>
       <c r="H6" t="n">
-        <v>19.94</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="n">
-        <v>46.07</v>
-      </c>
-      <c r="D7" t="n">
-        <v>46.07</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>541</v>
-      </c>
-      <c r="G7" t="n">
-        <v>24923</v>
-      </c>
-      <c r="H7" t="n">
         <v>24.92</v>
       </c>
     </row>

--- a/output/tables/universal_sm_hybrid/hybrid_headline.xlsx
+++ b/output/tables/universal_sm_hybrid/hybrid_headline.xlsx
@@ -419,22 +419,22 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>46.07</v>
+        <v>44.47</v>
       </c>
       <c r="D2" t="n">
-        <v>27.54</v>
+        <v>26.23</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5978</v>
+        <v>0.5898</v>
       </c>
       <c r="F2" t="n">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="G2" t="n">
-        <v>14946</v>
+        <v>14146</v>
       </c>
       <c r="H2" t="n">
-        <v>14.95</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="3">
@@ -445,22 +445,22 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>15.99</v>
+        <v>15.22</v>
       </c>
       <c r="D3" t="n">
-        <v>9.56</v>
+        <v>8.98</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5979</v>
+        <v>0.5897</v>
       </c>
       <c r="F3" t="n">
         <v>524</v>
       </c>
       <c r="G3" t="n">
-        <v>5011</v>
+        <v>4706</v>
       </c>
       <c r="H3" t="n">
-        <v>5.01</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="4">
@@ -471,22 +471,22 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>30.07</v>
+        <v>29.25</v>
       </c>
       <c r="D4" t="n">
-        <v>17.98</v>
+        <v>17.25</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5979</v>
+        <v>0.5897</v>
       </c>
       <c r="F4" t="n">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="G4" t="n">
-        <v>9935</v>
+        <v>9440</v>
       </c>
       <c r="H4" t="n">
-        <v>9.94</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="5">
@@ -497,22 +497,22 @@
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>46.07</v>
+        <v>44.47</v>
       </c>
       <c r="D5" t="n">
-        <v>36.85</v>
+        <v>35.58</v>
       </c>
       <c r="E5" t="n">
         <v>0.8</v>
       </c>
       <c r="F5" t="n">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G5" t="n">
-        <v>19938</v>
+        <v>19092</v>
       </c>
       <c r="H5" t="n">
-        <v>19.94</v>
+        <v>19.09</v>
       </c>
     </row>
     <row r="6">
@@ -523,22 +523,22 @@
         <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>46.07</v>
+        <v>44.47</v>
       </c>
       <c r="D6" t="n">
-        <v>46.07</v>
+        <v>44.47</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G6" t="n">
-        <v>24923</v>
+        <v>23866</v>
       </c>
       <c r="H6" t="n">
-        <v>24.92</v>
+        <v>23.87</v>
       </c>
     </row>
   </sheetData>

--- a/output/tables/universal_sm_hybrid/hybrid_headline.xlsx
+++ b/output/tables/universal_sm_hybrid/hybrid_headline.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="scenarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="seed_variants" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">scenario</t>
   </si>
@@ -38,6 +39,21 @@
     <t xml:space="preserve">annual_cost_B_USD</t>
   </si>
   <si>
+    <t xml:space="preserve">seed_recipients_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed_cost_M_USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed_cost_B_USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_cost_incl_seed_M_USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_cost_incl_seed_B_USD</t>
+  </si>
+  <si>
     <t xml:space="preserve">headline_sipp_observed_conditional</t>
   </si>
   <si>
@@ -57,6 +73,33 @@
   </si>
   <si>
     <t xml:space="preserve">sens_full_participation_100pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed_variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recipients_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">full_amount_recipients_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avg_seed_per_recipient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bottom3_decile_share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pro_rata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flat_then_taper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extended_taper</t>
   </si>
 </sst>
 </file>
@@ -410,13 +453,28 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>44.47</v>
@@ -436,13 +494,28 @@
       <c r="H2" t="n">
         <v>14.15</v>
       </c>
+      <c r="I2" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4447</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L2" t="n">
+        <v>18593</v>
+      </c>
+      <c r="M2" t="n">
+        <v>18.59</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>15.22</v>
@@ -462,13 +535,28 @@
       <c r="H3" t="n">
         <v>4.71</v>
       </c>
+      <c r="I3" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1522</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6228</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>29.25</v>
@@ -488,13 +576,28 @@
       <c r="H4" t="n">
         <v>9.44</v>
       </c>
+      <c r="I4" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2925</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L4" t="n">
+        <v>12365</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12.37</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>44.47</v>
@@ -514,13 +617,28 @@
       <c r="H5" t="n">
         <v>19.09</v>
       </c>
+      <c r="I5" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4447</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L5" t="n">
+        <v>23540</v>
+      </c>
+      <c r="M5" t="n">
+        <v>23.54</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>44.47</v>
@@ -539,6 +657,147 @@
       </c>
       <c r="H6" t="n">
         <v>23.87</v>
+      </c>
+      <c r="I6" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4447</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>28313</v>
+      </c>
+      <c r="M6" t="n">
+        <v>28.31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4447</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7898</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1709</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="D3" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9089</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3643</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="D4" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="F4" t="n">
+        <v>82</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8451</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5270</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="D5" t="n">
+        <v>60.31</v>
+      </c>
+      <c r="E5" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="F5" t="n">
+        <v>87</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7416</v>
       </c>
     </row>
   </sheetData>
